--- a/KURIKULUM2026_REVISI/039_LAMPIRAN_SIAP_BUKU_KPT_SISTEKIN_2026.xlsx
+++ b/KURIKULUM2026_REVISI/039_LAMPIRAN_SIAP_BUKU_KPT_SISTEKIN_2026.xlsx
@@ -3584,7 +3584,7 @@
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>STI-521 IoT; STI-626 Smart City</t>
+          <t>STI-521 IoT; STI-726 Smart City</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="B218" s="7" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B220" s="7" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="B287" s="7" t="inlineStr">
         <is>
-          <t>STI-624</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C287" s="8" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B288" s="9" t="inlineStr">
         <is>
-          <t>STI-625</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C288" s="10" t="inlineStr">
@@ -8200,7 +8200,7 @@
       </c>
       <c r="B289" s="7" t="inlineStr">
         <is>
-          <t>STI-626</t>
+          <t>STI-726</t>
         </is>
       </c>
       <c r="C289" s="8" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B290" s="9" t="inlineStr">
         <is>
-          <t>STI-627</t>
+          <t>STI-727</t>
         </is>
       </c>
       <c r="C290" s="10" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G314" s="10" t="inlineStr">
         <is>
-          <t>STI-413, STI-624</t>
+          <t>STI-413, STI-726</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="G316" s="10" t="inlineStr">
         <is>
-          <t>STI-626, STI-521</t>
+          <t>STI-726, STI-521</t>
         </is>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="E383" s="10" t="inlineStr">
         <is>
-          <t>Konversi ke STI-625 Smart City (2) + PKL + MK pengabdian</t>
+          <t>Konversi ke STI-727 Smart City (2) + PKL + MK pengabdian</t>
         </is>
       </c>
     </row>
